--- a/experiments/sleet_experiments.xlsx
+++ b/experiments/sleet_experiments.xlsx
@@ -238,8 +238,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SleetExperiments" displayName="SleetExperiments" ref="A1:L6" totalsRowShown="0">
-  <autoFilter ref="A1:L6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SleetExperiments" displayName="SleetExperiments" ref="A1:L14" totalsRowShown="0">
+  <autoFilter ref="A1:L14">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -273,7 +273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -341,23 +341,35 @@
       <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>17</v>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>37.7688</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>18.6358</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>56.4593</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>32.7091</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>18.6905</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>14.0733</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -379,23 +391,35 @@
       <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>17</v>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>44.8565</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>24.2250</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>60.6656</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>43.1573</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>15.8091</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>18.9323</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -417,23 +441,35 @@
       <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>17</v>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>7.2298</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>0.4963</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>24.8337</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>14.7422</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>17.6039</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>14.2459</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -455,23 +491,35 @@
       <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>17</v>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>87.8362</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>54.9907</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>90.1296</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>51.9119</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2.2934</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>-3.0788</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -515,45 +563,483 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>17</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>group6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>37.0826</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>17.5364</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>45.2561</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>28.0748</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>8.1735</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>10.5384</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>group7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>45.1738</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>21.1453</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>58.7532</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>44.5311</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>13.5794</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>23.3858</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>group8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>14.0814</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>0.4508</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>25.4790</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>16.0477</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>11.3976</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>15.5969</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>group9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>87.9270</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>49.8882</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>86.4712</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>42.9374</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>-1.4558</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>-6.9508</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>group10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>37.5225</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>17.3188</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>45.8949</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>28.7702</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>8.3724</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>11.4514</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>group11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>46.4293</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>19.2971</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>63.8341</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>42.5679</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>17.4048</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>23.2708</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>group12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>16.6642</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1.3221</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>30.6813</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>18.0495</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>14.0171</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>16.7274</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>group13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>88.4206</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>42.8729</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>83.2107</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>46.0644</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>-5.2099</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>3.1915</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>average(12)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>10.0563</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>11.7820</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
